--- a/flare-pwr/SMR_Case/CaseMSLB_in.xlsx
+++ b/flare-pwr/SMR_Case/CaseMSLB_in.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b11560d98c47b3/Documents/Current Work Activities/FLASH Model/Integrated Model/FLARE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b11560d98c47b3/Documents/Current Work Activities/FLASH Model/Integrated Model/flare-pwr/SMR_Case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_3C4A02E3575A44CFEB3B98154B5DCE3A774CCA6D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A41B5515-4E31-42AF-B12D-C5FB78C230EF}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_3C4A02E3575A44CFEB3B98154B5DCE3A774CCA6D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFA0D8D5-5DB4-4304-82B9-AB25065C890C}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="-10860" windowWidth="19155" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="-11340" windowWidth="16665" windowHeight="9765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CaseMSLB_in" sheetId="1" r:id="rId1"/>
